--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,14 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_E07E6E6E40A7874E7976767C652B3F0259D18FF9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Clients" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Cases" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Activities" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Templates" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Settings" state="visible" r:id="rId8"/>
+    <sheet name="Clients" sheetId="1" r:id="rId1"/>
+    <sheet name="Cases" sheetId="2" r:id="rId2"/>
+    <sheet name="Activities" sheetId="3" r:id="rId3"/>
+    <sheet name="Templates" sheetId="4" r:id="rId4"/>
+    <sheet name="Settings" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -257,24 +261,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <sz val="11"/>
       <color rgb="FF14201F"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -673,9 +677,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -685,7 +689,7 @@
     <col min="6" max="6" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -705,7 +709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -726,16 +730,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:F2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
@@ -747,7 +751,7 @@
     <col min="10" max="10" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -779,7 +783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
@@ -811,7 +815,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -844,16 +848,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J3" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
@@ -865,7 +869,7 @@
     <col min="9" max="9" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -894,7 +898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
@@ -923,7 +927,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
@@ -953,22 +957,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I3" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -979,7 +983,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>52</v>
       </c>
@@ -990,7 +994,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>55</v>
       </c>
@@ -1001,7 +1005,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>58</v>
       </c>
@@ -1012,7 +1016,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>61</v>
       </c>
@@ -1023,7 +1027,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>64</v>
       </c>
@@ -1035,22 +1039,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -1058,7 +1062,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>69</v>
       </c>
@@ -1066,7 +1070,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>71</v>
       </c>
@@ -1074,7 +1078,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
@@ -1082,7 +1086,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>75</v>
       </c>
@@ -1090,7 +1094,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>77</v>
       </c>
@@ -1099,8 +1103,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B6" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>